--- a/data/trans_dic/P22$ss-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,81; 91,83</t>
+          <t>85,97; 91,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,18; 90,0</t>
+          <t>82,78; 89,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,34; 87,86</t>
+          <t>80,59; 87,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88,16; 92,98</t>
+          <t>88,11; 93,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,44; 92,57</t>
+          <t>85,62; 92,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,21; 92,78</t>
+          <t>85,46; 92,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,73; 90,55</t>
+          <t>84,01; 91,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,08; 92,67</t>
+          <t>88,28; 92,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,57; 91,23</t>
+          <t>87,05; 91,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85,34; 90,42</t>
+          <t>85,33; 90,4</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83,12; 88,44</t>
+          <t>83,2; 88,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,92; 92,47</t>
+          <t>88,72; 92,25</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,07; 91,3</t>
+          <t>84,09; 90,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,76; 86,64</t>
+          <t>78,07; 86,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,43; 88,61</t>
+          <t>80,77; 88,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,33; 92,07</t>
+          <t>86,01; 91,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,92; 96,38</t>
+          <t>90,93; 96,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,45; 95,44</t>
+          <t>88,82; 95,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,79; 95,37</t>
+          <t>89,8; 95,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,46; 96,38</t>
+          <t>92,66; 96,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,59; 93,05</t>
+          <t>88,64; 92,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83,97; 89,56</t>
+          <t>83,93; 89,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86,05; 90,87</t>
+          <t>86,29; 90,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,58; 93,44</t>
+          <t>89,78; 93,39</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,79; 99,68</t>
+          <t>97,76; 99,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,83; 99,7</t>
+          <t>97,89; 99,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97,44; 99,68</t>
+          <t>97,58; 99,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99,88; 100,0</t>
+          <t>99,84; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,53; 98,03</t>
+          <t>91,55; 98,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,59; 98,79</t>
+          <t>93,19; 98,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,46; 99,37</t>
+          <t>93,56; 99,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,6; 99,59</t>
+          <t>96,61; 99,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>96,95; 99,09</t>
+          <t>97,0; 99,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97,2; 99,14</t>
+          <t>97,19; 99,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97,18; 99,32</t>
+          <t>97,09; 99,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99,3; 99,97</t>
+          <t>99,23; 99,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>98,03; 99,33</t>
+          <t>97,99; 99,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>99,0; 99,83</t>
+          <t>98,95; 99,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,18; 98,86</t>
+          <t>97,18; 98,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98,29; 99,59</t>
+          <t>98,44; 99,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,01; 97,92</t>
+          <t>95,19; 97,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,29; 98,76</t>
+          <t>96,36; 98,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,54; 98,68</t>
+          <t>96,48; 98,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>98,7; 99,7</t>
+          <t>98,71; 99,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97,33; 98,66</t>
+          <t>97,38; 98,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98,21; 99,28</t>
+          <t>98,2; 99,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97,31; 98,61</t>
+          <t>97,2; 98,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,74; 99,52</t>
+          <t>98,66; 99,5</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,04; 98,22</t>
+          <t>94,3; 98,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,48; 99,5</t>
+          <t>97,47; 99,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98,34; 99,83</t>
+          <t>98,45; 99,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98,79; 99,97</t>
+          <t>98,74; 99,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,71; 98,07</t>
+          <t>94,63; 97,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,47; 99,33</t>
+          <t>97,81; 99,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,52; 99,84</t>
+          <t>98,59; 99,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>98,51; 99,63</t>
+          <t>98,45; 99,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,28; 97,8</t>
+          <t>95,09; 97,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98,01; 99,28</t>
+          <t>98,06; 99,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98,82; 99,73</t>
+          <t>98,78; 99,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,92; 99,68</t>
+          <t>98,93; 99,67</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,36; 97,91</t>
+          <t>93,56; 97,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,47; 96,96</t>
+          <t>90,63; 97,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,76; 98,2</t>
+          <t>93,7; 98,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88,44; 98,76</t>
+          <t>88,5; 98,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94,81; 97,01</t>
+          <t>94,79; 97,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,37; 97,73</t>
+          <t>95,37; 97,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,12; 98,24</t>
+          <t>96,24; 98,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95,63; 98,12</t>
+          <t>95,56; 98,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,93; 96,91</t>
+          <t>94,94; 96,94</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,92; 97,26</t>
+          <t>94,93; 97,19</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>96,15; 98,04</t>
+          <t>96,09; 97,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,97; 97,85</t>
+          <t>94,8; 97,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,02; 96,43</t>
+          <t>95,07; 96,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,38; 96,09</t>
+          <t>94,4; 96,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94,36; 95,87</t>
+          <t>94,3; 95,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95,73; 97,36</t>
+          <t>95,73; 97,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,68; 96,18</t>
+          <t>94,71; 96,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,61; 97,01</t>
+          <t>95,64; 96,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,78; 97,01</t>
+          <t>95,77; 97,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,64; 97,79</t>
+          <t>96,7; 97,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,06; 96,09</t>
+          <t>95,09; 96,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,28; 96,31</t>
+          <t>95,26; 96,31</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95,22; 96,26</t>
+          <t>95,33; 96,32</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,38; 97,38</t>
+          <t>96,44; 97,41</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>405265; 433690</t>
+          <t>406000; 434049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>363685; 393501</t>
+          <t>361936; 393299</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>344732; 376997</t>
+          <t>345797; 376499</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>445401; 469751</t>
+          <t>445157; 470287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>262033; 283896</t>
+          <t>262567; 283492</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>267955; 291744</t>
+          <t>268733; 291393</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>290590; 314265</t>
+          <t>291562; 316253</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>394123; 414669</t>
+          <t>395035; 414360</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674342; 710669</t>
+          <t>678083; 710971</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>641502; 679670</t>
+          <t>641381; 679477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>645119; 686401</t>
+          <t>645738; 687072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>847128; 880906</t>
+          <t>845252; 878833</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>308495; 334999</t>
+          <t>308565; 333632</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>325665; 362864</t>
+          <t>326940; 363511</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>302610; 333405</t>
+          <t>303919; 333862</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>390415; 416337</t>
+          <t>388958; 415572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>338095; 358388</t>
+          <t>338126; 357786</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>298977; 322612</t>
+          <t>300205; 323606</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>334271; 355040</t>
+          <t>334316; 354639</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>353729; 368724</t>
+          <t>354487; 368858</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>654478; 687481</t>
+          <t>654893; 686221</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>635509; 677793</t>
+          <t>635171; 678835</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>644112; 680207</t>
+          <t>645937; 680841</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>747798; 779994</t>
+          <t>749462; 779625</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>529580; 539836</t>
+          <t>529416; 539814</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>615783; 627530</t>
+          <t>616118; 627489</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>508542; 520268</t>
+          <t>509266; 520838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667432; 668264</t>
+          <t>667223; 668264</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>153568; 164485</t>
+          <t>153609; 164568</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>243461; 256986</t>
+          <t>242410; 256221</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>155253; 165084</t>
+          <t>155419; 165102</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>161239; 166231</t>
+          <t>161252; 166254</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>687697; 702878</t>
+          <t>688063; 702576</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>864650; 881896</t>
+          <t>864518; 881997</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>668656; 683377</t>
+          <t>667981; 683613</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>829358; 834944</t>
+          <t>828778; 834685</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1210832; 1226899</t>
+          <t>1210391; 1226952</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1146482; 1156085</t>
+          <t>1145864; 1155945</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1116263; 1135630</t>
+          <t>1116275; 1136455</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1017166; 1030558</t>
+          <t>1018645; 1030482</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>678608; 699424</t>
+          <t>679920; 699817</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>738237; 757172</t>
+          <t>738778; 756763</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>793874; 811430</t>
+          <t>793372; 811099</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>965365; 975138</t>
+          <t>965478; 975247</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1897494; 1923272</t>
+          <t>1898370; 1923968</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1890183; 1910903</t>
+          <t>1889964; 1911113</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1918074; 1943725</t>
+          <t>1915832; 1943794</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1987563; 2003247</t>
+          <t>1985914; 2002838</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>329677; 344307</t>
+          <t>330564; 344779</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>497732; 508064</t>
+          <t>497691; 508318</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609248; 618469</t>
+          <t>609925; 618491</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>469311; 474880</t>
+          <t>469053; 474722</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>538647; 557764</t>
+          <t>538211; 556539</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>742256; 756450</t>
+          <t>744849; 756615</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>726347; 736094</t>
+          <t>726890; 736377</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>826519; 835930</t>
+          <t>825998; 835888</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>875886; 899108</t>
+          <t>874182; 898367</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1246770; 1263013</t>
+          <t>1247477; 1263083</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1340800; 1353104</t>
+          <t>1340192; 1352790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1299890; 1309806</t>
+          <t>1300041; 1309683</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>277521; 291064</t>
+          <t>278128; 291167</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>241445; 258756</t>
+          <t>241875; 259022</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269235; 281982</t>
+          <t>269041; 281925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>212709; 237529</t>
+          <t>212858; 237100</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1182000; 1209477</t>
+          <t>1181735; 1209743</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1057962; 1084175</t>
+          <t>1057972; 1083733</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1038837; 1061687</t>
+          <t>1040160; 1061853</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>728087; 747075</t>
+          <t>727539; 747221</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1465651; 1496332</t>
+          <t>1465912; 1496731</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1306340; 1338545</t>
+          <t>1306423; 1337597</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1315264; 1341095</t>
+          <t>1314369; 1340049</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>951439; 980352</t>
+          <t>949772; 980918</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3101164; 3147145</t>
+          <t>3102960; 3148341</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3228766; 3287180</t>
+          <t>3229187; 3285338</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3191717; 3242878</t>
+          <t>3189958; 3243969</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3231972; 3287057</t>
+          <t>3232062; 3287490</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3196587; 3247180</t>
+          <t>3197649; 3245697</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3394147; 3443960</t>
+          <t>3395283; 3442180</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3376945; 3420201</t>
+          <t>3376816; 3423710</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3455327; 3496363</t>
+          <t>3457465; 3498651</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6312133; 6380561</t>
+          <t>6313934; 6380262</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6641916; 6714011</t>
+          <t>6640331; 6713498</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6578379; 6650402</t>
+          <t>6586084; 6653992</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6699529; 6769650</t>
+          <t>6704303; 6771332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$ss-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,97; 91,91</t>
+          <t>86,04; 91,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,78; 89,96</t>
+          <t>83,13; 90,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,59; 87,74</t>
+          <t>80,84; 88,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88,11; 93,09</t>
+          <t>88,48; 93,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,62; 92,44</t>
+          <t>85,35; 92,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,46; 92,67</t>
+          <t>85,59; 92,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,01; 91,12</t>
+          <t>83,8; 91,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>88,28; 92,6</t>
+          <t>88,36; 92,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>87,05; 91,27</t>
+          <t>86,76; 91,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85,33; 90,4</t>
+          <t>85,22; 90,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83,2; 88,52</t>
+          <t>83,38; 88,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,72; 92,25</t>
+          <t>89,24; 92,42</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>84,09; 90,92</t>
+          <t>84,23; 91,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>78,07; 86,8</t>
+          <t>77,82; 86,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,77; 88,73</t>
+          <t>81,18; 88,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,01; 91,9</t>
+          <t>85,93; 91,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,93; 96,21</t>
+          <t>91,48; 96,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,82; 95,74</t>
+          <t>88,65; 95,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,8; 95,26</t>
+          <t>89,77; 95,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,66; 96,41</t>
+          <t>92,91; 96,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,64; 92,88</t>
+          <t>88,67; 92,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83,93; 89,7</t>
+          <t>84,12; 89,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>86,29; 90,96</t>
+          <t>85,99; 90,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>89,78; 93,39</t>
+          <t>90,0; 93,45</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99,98%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>97,76; 99,68</t>
+          <t>97,8; 99,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,89; 99,69</t>
+          <t>97,75; 99,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97,58; 99,79</t>
+          <t>97,45; 99,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>99,84; 100,0</t>
+          <t>97,58; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,55; 98,08</t>
+          <t>91,31; 98,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>93,19; 98,5</t>
+          <t>93,76; 98,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,56; 99,39</t>
+          <t>93,75; 99,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,61; 99,61</t>
+          <t>96,83; 99,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97,0; 99,04</t>
+          <t>96,9; 99,07</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97,19; 99,15</t>
+          <t>97,32; 99,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97,09; 99,36</t>
+          <t>97,22; 99,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>99,23; 99,94</t>
+          <t>98,04; 99,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97,99; 99,33</t>
+          <t>98,05; 99,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>98,95; 99,82</t>
+          <t>98,93; 99,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97,18; 98,93</t>
+          <t>97,21; 98,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98,44; 99,58</t>
+          <t>97,56; 99,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,19; 97,97</t>
+          <t>95,06; 97,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,36; 98,71</t>
+          <t>96,27; 98,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48; 98,64</t>
+          <t>96,7; 98,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>98,71; 99,71</t>
+          <t>98,53; 99,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97,38; 98,69</t>
+          <t>97,41; 98,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98,2; 99,29</t>
+          <t>98,2; 99,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>97,2; 98,62</t>
+          <t>97,32; 98,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,66; 99,5</t>
+          <t>98,17; 99,34</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>94,3; 98,35</t>
+          <t>94,42; 98,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97,47; 99,55</t>
+          <t>97,5; 99,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>98,45; 99,83</t>
+          <t>98,44; 99,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98,74; 99,93</t>
+          <t>98,06; 99,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>94,63; 97,85</t>
+          <t>94,48; 97,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>97,81; 99,36</t>
+          <t>97,79; 99,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,59; 99,88</t>
+          <t>98,47; 99,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>98,45; 99,63</t>
+          <t>98,29; 99,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>95,09; 97,72</t>
+          <t>95,12; 97,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98,06; 99,29</t>
+          <t>97,96; 99,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98,78; 99,7</t>
+          <t>98,76; 99,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>98,93; 99,67</t>
+          <t>98,6; 99,53</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,56; 97,95</t>
+          <t>93,29; 98,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,63; 97,05</t>
+          <t>90,81; 97,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,7; 98,18</t>
+          <t>93,63; 98,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>88,5; 98,58</t>
+          <t>89,12; 98,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>94,79; 97,03</t>
+          <t>94,71; 97,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,37; 97,69</t>
+          <t>95,32; 97,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,24; 98,25</t>
+          <t>96,2; 98,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>95,56; 98,14</t>
+          <t>95,91; 98,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,94; 96,94</t>
+          <t>95,04; 97,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>94,93; 97,19</t>
+          <t>95,01; 97,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>96,09; 97,96</t>
+          <t>96,07; 97,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,8; 97,91</t>
+          <t>95,15; 97,88</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>95,07; 96,46</t>
+          <t>95,12; 96,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>94,4; 96,04</t>
+          <t>94,42; 96,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94,3; 95,9</t>
+          <t>94,29; 95,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>95,73; 97,38</t>
+          <t>95,34; 96,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,71; 96,14</t>
+          <t>94,65; 96,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,64; 96,96</t>
+          <t>95,55; 97,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,77; 97,1</t>
+          <t>95,78; 97,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>96,7; 97,85</t>
+          <t>96,54; 97,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,09; 96,09</t>
+          <t>95,06; 96,08</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95,26; 96,31</t>
+          <t>95,27; 96,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95,33; 96,32</t>
+          <t>95,28; 96,3</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,44; 97,41</t>
+          <t>96,21; 97,06</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>459482</t>
+          <t>503002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>405241</t>
+          <t>442529</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>864723</t>
+          <t>945531</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>406000; 434049</t>
+          <t>406341; 433956</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>361936; 393299</t>
+          <t>363441; 394432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>345797; 376499</t>
+          <t>346877; 377827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>445157; 470287</t>
+          <t>487190; 514488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>262567; 283492</t>
+          <t>261746; 283193</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>268733; 291393</t>
+          <t>269152; 291028</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>291562; 316253</t>
+          <t>290836; 316225</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>395035; 414360</t>
+          <t>431569; 452290</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>678083; 710971</t>
+          <t>675817; 711201</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>641381; 679477</t>
+          <t>640544; 680194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>645738; 687072</t>
+          <t>647181; 685475</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>845252; 878833</t>
+          <t>927271; 960310</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>403926</t>
+          <t>430660</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>362081</t>
+          <t>401639</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>766007</t>
+          <t>832299</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>308565; 333632</t>
+          <t>309081; 334032</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>326940; 363511</t>
+          <t>325915; 362803</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>303919; 333862</t>
+          <t>305451; 332991</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>388958; 415572</t>
+          <t>415215; 443975</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>338126; 357786</t>
+          <t>340182; 358795</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>300205; 323606</t>
+          <t>299638; 322396</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>334316; 354639</t>
+          <t>334192; 354951</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>354487; 368858</t>
+          <t>393155; 407809</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>654893; 686221</t>
+          <t>655103; 686787</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>635171; 678835</t>
+          <t>636616; 680299</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>645937; 680841</t>
+          <t>643642; 680464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>749462; 779625</t>
+          <t>815721; 846977</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668100</t>
+          <t>469266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>164515</t>
+          <t>185076</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>832614</t>
+          <t>654342</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>529416; 539814</t>
+          <t>529636; 539805</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>616118; 627489</t>
+          <t>615241; 627527</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>509266; 520838</t>
+          <t>508625; 520265</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667223; 668264</t>
+          <t>460192; 471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>153609; 164568</t>
+          <t>153195; 164484</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>242410; 256221</t>
+          <t>243885; 256267</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>155419; 165102</t>
+          <t>155746; 165093</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>161252; 166254</t>
+          <t>181554; 186811</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>688063; 702576</t>
+          <t>687386; 702766</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>864518; 881997</t>
+          <t>865705; 882418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>667981; 683613</t>
+          <t>668881; 683951</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>828778; 834685</t>
+          <t>646181; 657717</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1025610</t>
+          <t>1118208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>970960</t>
+          <t>853749</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1996569</t>
+          <t>1971957</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1210391; 1226952</t>
+          <t>1211139; 1227134</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1145864; 1155945</t>
+          <t>1145679; 1156057</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1116275; 1136455</t>
+          <t>1116624; 1136513</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1018645; 1030482</t>
+          <t>1104200; 1125356</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>679920; 699817</t>
+          <t>679025; 699248</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>738778; 756763</t>
+          <t>738072; 757365</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>793372; 811099</t>
+          <t>795224; 811872</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>965478; 975247</t>
+          <t>848551; 857022</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1898370; 1923968</t>
+          <t>1898978; 1923907</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1889964; 1911113</t>
+          <t>1890020; 1909885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1915832; 1943794</t>
+          <t>1918274; 1943771</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1985914; 2002838</t>
+          <t>1956522; 1979883</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473248</t>
+          <t>564535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>832310</t>
+          <t>822086</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1305557</t>
+          <t>1386621</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>330564; 344779</t>
+          <t>330997; 344739</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>497691; 508318</t>
+          <t>497815; 508465</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609925; 618491</t>
+          <t>609883; 618474</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>469053; 474722</t>
+          <t>556965; 567177</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>538211; 556539</t>
+          <t>537330; 556924</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>744849; 756615</t>
+          <t>744700; 757463</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>726890; 736377</t>
+          <t>725956; 736288</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>825998; 835888</t>
+          <t>815964; 825705</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>874182; 898367</t>
+          <t>874415; 898370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1247477; 1263083</t>
+          <t>1246120; 1262943</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1340192; 1352790</t>
+          <t>1339977; 1352706</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1300041; 1309683</t>
+          <t>1378481; 1391556</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>229354</t>
+          <t>225204</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>740272</t>
+          <t>821856</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>969626</t>
+          <t>1047060</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>278128; 291167</t>
+          <t>277312; 291483</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>241875; 259022</t>
+          <t>242360; 259168</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269041; 281925</t>
+          <t>268854; 282000</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>212858; 237100</t>
+          <t>211414; 233320</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1181735; 1209743</t>
+          <t>1180769; 1209574</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1057972; 1083733</t>
+          <t>1057413; 1084114</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1040160; 1061853</t>
+          <t>1039647; 1061862</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>727539; 747221</t>
+          <t>809765; 829537</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1465912; 1496731</t>
+          <t>1467433; 1497706</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1306423; 1337597</t>
+          <t>1307589; 1339101</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1314369; 1340049</t>
+          <t>1314193; 1340045</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>949772; 980918</t>
+          <t>1029109; 1058550</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3259718</t>
+          <t>3310873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3475378</t>
+          <t>3526936</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6735097</t>
+          <t>6837809</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3102960; 3148341</t>
+          <t>3104437; 3152360</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3229187; 3285338</t>
+          <t>3230037; 3286960</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3189958; 3243969</t>
+          <t>3189413; 3242401</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3232062; 3287490</t>
+          <t>3281891; 3334419</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3197649; 3245697</t>
+          <t>3195369; 3244759</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3395283; 3442180</t>
+          <t>3392167; 3444035</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3376816; 3423710</t>
+          <t>3377048; 3422907</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3457465; 3498651</t>
+          <t>3508861; 3544236</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6313934; 6380262</t>
+          <t>6312019; 6379391</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6640331; 6713498</t>
+          <t>6640977; 6718555</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6586084; 6653992</t>
+          <t>6582467; 6653016</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6704303; 6771332</t>
+          <t>6809211; 6869379</t>
         </is>
       </c>
     </row>
